--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N162_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N162_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.74541331819765</v>
+        <v>7.921129664207118</v>
       </c>
       <c r="D2" t="n">
-        <v>94.84632022159511</v>
+        <v>15.41252703600921</v>
       </c>
       <c r="E2" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F2" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.02721290142279</v>
+        <v>5.854422096481203</v>
       </c>
       <c r="D3" t="n">
-        <v>81.61491348259447</v>
+        <v>13.2624234409216</v>
       </c>
       <c r="E3" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F3" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.26021409502108</v>
+        <v>9.792284790440926</v>
       </c>
       <c r="D4" t="n">
-        <v>77.88468320079443</v>
+        <v>12.6562610201291</v>
       </c>
       <c r="E4" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F4" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.87904945828093</v>
+        <v>8.917845536970651</v>
       </c>
       <c r="D5" t="n">
-        <v>67.04461477062482</v>
+        <v>10.89474990022653</v>
       </c>
       <c r="E5" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F5" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.26180363382078</v>
+        <v>5.892543090495876</v>
       </c>
       <c r="D6" t="n">
-        <v>51.9495796884928</v>
+        <v>8.441806699380081</v>
       </c>
       <c r="E6" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F6" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.22076664416584</v>
+        <v>6.53587457967695</v>
       </c>
       <c r="D7" t="n">
-        <v>43.50971818781704</v>
+        <v>7.070329205520269</v>
       </c>
       <c r="E7" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F7" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>49.43089139290223</v>
+        <v>8.032519851346612</v>
       </c>
       <c r="D8" t="n">
-        <v>52.50973473941377</v>
+        <v>8.532831895154738</v>
       </c>
       <c r="E8" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F8" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>57.71491254872624</v>
+        <v>9.378673289168015</v>
       </c>
       <c r="D9" t="n">
-        <v>60.47429746812702</v>
+        <v>9.82707333857064</v>
       </c>
       <c r="E9" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F9" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>51.96245265906708</v>
+        <v>8.4438985570984</v>
       </c>
       <c r="D10" t="n">
-        <v>49.33361863439654</v>
+        <v>8.016713028089438</v>
       </c>
       <c r="E10" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F10" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>52.81702838201365</v>
+        <v>8.582767112077219</v>
       </c>
       <c r="D11" t="n">
-        <v>57.01155197594034</v>
+        <v>9.264377196090306</v>
       </c>
       <c r="E11" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F11" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>51.47918106653234</v>
+        <v>8.365366923311505</v>
       </c>
       <c r="D12" t="n">
-        <v>48.85451870869162</v>
+        <v>7.938859290162389</v>
       </c>
       <c r="E12" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F12" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>43.52778885697937</v>
+        <v>7.073265689259148</v>
       </c>
       <c r="D13" t="n">
-        <v>49.20573930477118</v>
+        <v>7.995932637025317</v>
       </c>
       <c r="E13" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F13" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>37.65634076752546</v>
+        <v>6.119155374722888</v>
       </c>
       <c r="D14" t="n">
-        <v>40.26617359681481</v>
+        <v>6.543253209482407</v>
       </c>
       <c r="E14" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F14" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>9.990466819792552</v>
+        <v>1.62345085821629</v>
       </c>
       <c r="D15" t="n">
-        <v>35.83252144599293</v>
+        <v>5.822784734973852</v>
       </c>
       <c r="E15" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F15" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>23.75394704043941</v>
+        <v>3.860016394071404</v>
       </c>
       <c r="D16" t="n">
-        <v>40.04908730598494</v>
+        <v>6.507976687222553</v>
       </c>
       <c r="E16" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F16" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>31.20165705179419</v>
+        <v>5.070269270916556</v>
       </c>
       <c r="D17" t="n">
-        <v>51.05326791401561</v>
+        <v>8.296156036027536</v>
       </c>
       <c r="E17" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F17" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>8.665700119020782</v>
+        <v>1.408176269340877</v>
       </c>
       <c r="D18" t="n">
-        <v>8.049785547038898</v>
+        <v>1.308090151393821</v>
       </c>
       <c r="E18" t="n">
-        <v>14.96903088580196</v>
+        <v>2.432467518942819</v>
       </c>
       <c r="F18" t="n">
-        <v>19.15799219601134</v>
+        <v>3.113173731851844</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
